--- a/outputs/38462.xlsx
+++ b/outputs/38462.xlsx
@@ -315,7 +315,6 @@
         <v>2046.72916666667</v>
       </c>
       <c r="C1" s="1" t="n">
-        <f aca="false">CEILING(B1*24,1)</f>
         <v>49122</v>
       </c>
     </row>
@@ -327,7 +326,6 @@
         <v>2055.49861111111</v>
       </c>
       <c r="C2" s="1" t="n">
-        <f aca="false">CEILING(B2*24,1)</f>
         <v>49332</v>
       </c>
     </row>

--- a/outputs/38462.xlsx
+++ b/outputs/38462.xlsx
@@ -315,6 +315,7 @@
         <v>2046.72916666667</v>
       </c>
       <c r="C1" s="1" t="n">
+        <f aca="false">CEILING(B1*24,1)</f>
         <v>49122</v>
       </c>
     </row>
@@ -326,6 +327,7 @@
         <v>2055.49861111111</v>
       </c>
       <c r="C2" s="1" t="n">
+        <f aca="false">CEILING(B2*24,1)</f>
         <v>49332</v>
       </c>
     </row>
